--- a/order_forms/030_single_product_w_single_choice_orders--order_forms.xlsx
+++ b/order_forms/030_single_product_w_single_choice_orders--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67890</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67890</t>
+          <t>98765</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>98765</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>98765</t>
+          <t>11111</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>98765</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>98765</t>
+          <t>22222</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>33333</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>22222</t>
+          <t>44444</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>55555</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>55555</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>66666</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44444</t>
+          <t>66666</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>77777</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>77777</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>88888</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>66666</t>
+          <t>88888</t>
         </is>
       </c>
     </row>
@@ -1231,46 +1231,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>77777</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>77777</t>
+          <t>99999</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>customer_id_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>88888</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>88888</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>customer_id_choices</t>
+          <t>order_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rejected</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Finished</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cancelled</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>finished</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finished</t>
+          <t>Shipping</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1384,129 +1384,61 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lost</t>
+          <t>Shipping</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>shipping_method_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>express_shipping</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>order_status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>lost</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Lost</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>shipping_method_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Pickup</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>shipping_method_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Shipping</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>shipping_method_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>express_shipping</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Express Shipping</t>
         </is>
